--- a/templates/excel-templates/experimentSamples.Neutralizing_Antibody_Titer.xlsx
+++ b/templates/excel-templates/experimentSamples.Neutralizing_Antibody_Titer.xlsx
@@ -177,7 +177,7 @@
     <t>neutralizing_antibody_titer</t>
   </si>
   <si>
-    <t>Schema Version 3.34</t>
+    <t>Schema Version 3.35</t>
   </si>
   <si>
     <t>Please do not delete or edit this column</t>

--- a/templates/excel-templates/experimentSamples.Neutralizing_Antibody_Titer.xlsx
+++ b/templates/excel-templates/experimentSamples.Neutralizing_Antibody_Titer.xlsx
@@ -177,7 +177,7 @@
     <t>neutralizing_antibody_titer</t>
   </si>
   <si>
-    <t>Schema Version 3.35</t>
+    <t>Schema Version 3.36</t>
   </si>
   <si>
     <t>Please do not delete or edit this column</t>
